--- a/test_data/excel/afe-lines-valid.xlsx
+++ b/test_data/excel/afe-lines-valid.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="requirement-items" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="afe-lines" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:P3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -449,35 +449,50 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>section_name</t>
+          <t>hole_section_code</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
+          <t>rate_basis</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>daily_consumption</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>quantity_override_reason</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
           <t>planned_duration_days</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>planned_depth_from</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>planned_depth_to</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>depth_unit_code</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>notes</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>is_active</t>
         </is>
@@ -503,7 +518,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -512,29 +527,34 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>17.5 inch</t>
-        </is>
-      </c>
-      <c r="H2" t="n">
+          <t>17-1/2</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>daily</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
         <v>5</v>
       </c>
-      <c r="I2" t="n">
+      <c r="L2" t="n">
         <v>0</v>
       </c>
-      <c r="J2" t="n">
+      <c r="M2" t="n">
         <v>1200</v>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>Synthetic requirement</t>
-        </is>
-      </c>
-      <c r="M2" t="b">
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>Synthetic service line</t>
+        </is>
+      </c>
+      <c r="P2" t="b">
         <v>1</v>
       </c>
     </row>
@@ -544,12 +564,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>MAT-001</t>
+          <t>MUD-001</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>material</t>
+          <t>mud_chemical</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -557,9 +577,6 @@
           <t>CC-001</t>
         </is>
       </c>
-      <c r="E3" t="n">
-        <v>100</v>
-      </c>
       <c r="F3" t="inlineStr">
         <is>
           <t>EA</t>
@@ -567,26 +584,37 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>12.25 inch</t>
+          <t>12-1/4</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>daily_consumption</t>
         </is>
       </c>
       <c r="I3" t="n">
+        <v>20</v>
+      </c>
+      <c r="K3" t="n">
+        <v>6</v>
+      </c>
+      <c r="L3" t="n">
         <v>1200</v>
       </c>
-      <c r="J3" t="n">
+      <c r="M3" t="n">
         <v>2500</v>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>M</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>Synthetic material</t>
-        </is>
-      </c>
-      <c r="M3" t="b">
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Computed from 20/day x 6 days</t>
+        </is>
+      </c>
+      <c r="P3" t="b">
         <v>1</v>
       </c>
     </row>
